--- a/artifacts/manual_spots/manual_spots.xlsx
+++ b/artifacts/manual_spots/manual_spots.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,10 +440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="C2" t="n">
-        <v>1046</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3">
@@ -453,36 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1067</v>
+        <v>475</v>
       </c>
       <c r="C3" t="n">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>976</v>
-      </c>
-      <c r="C4" t="n">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1328</v>
-      </c>
-      <c r="C5" t="n">
-        <v>696</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
